--- a/education_forms/049_salad_ingredients_knowledge_quiz--education_forms.xlsx
+++ b/education_forms/049_salad_ingredients_knowledge_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'lettuce'}</t>
+          <t>lettuce</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'lettuce'}</t>
+          <t>lettuce</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tomato'}</t>
+          <t>tomato</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'tomato'}</t>
+          <t>tomato</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cucumber'}</t>
+          <t>cucumber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'cucumber'}</t>
+          <t>cucumber</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'carrot'}</t>
+          <t>carrot</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'carrot'}</t>
+          <t>carrot</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'beet'}</t>
+          <t>beet</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'beet'}</t>
+          <t>beet</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'onion'}</t>
+          <t>onion</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'onion'}</t>
+          <t>onion</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'bell_pepper'}</t>
+          <t>bell_pepper</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'bell_pepper'}</t>
+          <t>bell pepper</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'celery'}</t>
+          <t>celery</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'celery'}</t>
+          <t>celery</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'plain'}</t>
+          <t>plain</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'plain'}</t>
+          <t>plain</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'with_dressing'}</t>
+          <t>with_dressing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'with_dressing'}</t>
+          <t>with dressing</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'with_cheese'}</t>
+          <t>with_cheese</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'with_cheese'}</t>
+          <t>with cheese</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'with_fruits'}</t>
+          <t>with_fruits</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'with_fruits'}</t>
+          <t>with fruits</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'with_nuts'}</t>
+          <t>with_nuts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'with_nuts'}</t>
+          <t>with nuts</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'mayonnaise'}</t>
+          <t>mayonnaise</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'mayonnaise'}</t>
+          <t>mayonnaise</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'ranch'}</t>
+          <t>ranch</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'ranch'}</t>
+          <t>ranch</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'thousand_island_dressing'}</t>
+          <t>thousand_island_dressing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'thousand_island_dressing'}</t>
+          <t>thousand island dressing</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'balsamic_vinagerre'}</t>
+          <t>balsamic_vinagerre</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'balsamic_vinagerre'}</t>
+          <t>balsamic vinagerre</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'blue_cheese'}</t>
+          <t>blue_cheese</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'blue_cheese'}</t>
+          <t>blue cheese</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'caesar'}</t>
+          <t>caesar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'caesar'}</t>
+          <t>caesar</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'ranch'}</t>
+          <t>homemade</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'ranch'}</t>
+          <t>homemade</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>quiz_question_3_choices</t>
+          <t>quiz_question_4_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'homemade'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'homemade'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>quiz_question_4_choices</t>
+          <t>quiz_question_9_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>quiz_question_9_choices</t>
+          <t>quiz_question_10_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1556,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>quiz_question_10_choices</t>
+          <t>quiz_question_11_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1590,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>quiz_question_11_choices</t>
+          <t>quiz_question_12_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1624,29 +1624,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>quiz_question_12_choices</t>
+          <t>quiz_question_13_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1658,29 +1658,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>quiz_question_13_choices</t>
+          <t>quiz_question_14_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1692,29 +1692,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>quiz_question_14_choices</t>
+          <t>quiz_question_15_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1726,29 +1726,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>quiz_question_15_choices</t>
+          <t>quiz_question_16_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1760,29 +1760,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>quiz_question_16_choices</t>
+          <t>quiz_question_17_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1794,29 +1794,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>quiz_question_17_choices</t>
+          <t>quiz_question_18_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1828,29 +1828,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quiz_question_18_choices</t>
+          <t>quiz_question_19_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1862,29 +1862,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>quiz_question_19_choices</t>
+          <t>quiz_question_20_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1896,29 +1896,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>quiz_question_20_choices</t>
+          <t>quiz_question_21_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1930,27 +1930,10 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>quiz_question_21_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
         <is>
           <t>No</t>
         </is>
